--- a/data/rooms.xlsx
+++ b/data/rooms.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,51 +502,6 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>Office</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>E-301</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Lab-1</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Laboratory</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Lab-2</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Laboratory</t>
         </is>
       </c>
     </row>
